--- a/backend/output/template/模板.xlsx
+++ b/backend/output/template/模板.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangkai/ProjectWorkspace/Fastapi-Vue/Krun/backend/output/template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangkai/ProjectWorkspace/Fastapi-Vue/KeenRunner/backend/output/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1D5BA8-DFBF-6142-9285-8FCD11913B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395B56C7-229C-EE4F-8EAE-F1A2CEACB8C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="48200" yWindow="7360" windowWidth="28580" windowHeight="17440" xr2:uid="{B4CDD553-F6E2-E74E-A789-E7CE3B2875FD}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
   <si>
     <t>场景1名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -57,10 +57,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ASSERT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>xpath.field1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -194,8 +190,26 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>ASSERT_HEAD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASSERT_BODY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>message</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>field1</t>
+  </si>
+  <si>
+    <t>field2</t>
   </si>
 </sst>
 </file>
@@ -260,18 +274,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -587,8 +604,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C401589C-A87D-0D49-B83B-478A1235A391}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26"/>
+  <cols>
+    <col min="1" max="1" width="13.08984375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" style="4" customWidth="1"/>
+    <col min="4" max="5" width="10.6328125" style="4"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1"/>
@@ -602,7 +625,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -616,87 +639,87 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -710,24 +733,24 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1">
         <v>18</v>
@@ -744,24 +767,24 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="1">
         <v>4224</v>
@@ -778,7 +801,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -787,27 +810,80 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
+      <c r="C18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>42</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
